--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>136011988</v>
       </c>
       <c r="B115" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>136012010</v>
       </c>
       <c r="B116" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>136012013</v>
       </c>
       <c r="B117" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136012022</v>
       </c>
       <c r="B120" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>136012027</v>
       </c>
       <c r="B121" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136012030</v>
       </c>
       <c r="B122" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>136012003</v>
       </c>
       <c r="B126" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>136012036</v>
       </c>
       <c r="B127" t="n">
-        <v>58601</v>
+        <v>58603</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>136012008</v>
       </c>
       <c r="B168" t="n">
-        <v>56544</v>
+        <v>56546</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>136011988</v>
       </c>
       <c r="B115" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>136012010</v>
       </c>
       <c r="B116" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>136012013</v>
       </c>
       <c r="B117" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136012022</v>
       </c>
       <c r="B120" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>136012027</v>
       </c>
       <c r="B121" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136012030</v>
       </c>
       <c r="B122" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>136012003</v>
       </c>
       <c r="B126" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>136012036</v>
       </c>
       <c r="B127" t="n">
-        <v>58603</v>
+        <v>58604</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>136012008</v>
       </c>
       <c r="B168" t="n">
-        <v>56546</v>
+        <v>56547</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>136011988</v>
       </c>
       <c r="B115" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>136012010</v>
       </c>
       <c r="B116" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>136012013</v>
       </c>
       <c r="B117" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136012022</v>
       </c>
       <c r="B120" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>136012027</v>
       </c>
       <c r="B121" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136012030</v>
       </c>
       <c r="B122" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>136012003</v>
       </c>
       <c r="B126" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>136012036</v>
       </c>
       <c r="B127" t="n">
-        <v>58604</v>
+        <v>58608</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>136012008</v>
       </c>
       <c r="B168" t="n">
-        <v>56547</v>
+        <v>56551</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>136011988</v>
       </c>
       <c r="B115" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>136012010</v>
       </c>
       <c r="B116" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>136012013</v>
       </c>
       <c r="B117" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136012022</v>
       </c>
       <c r="B120" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>136012027</v>
       </c>
       <c r="B121" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136012030</v>
       </c>
       <c r="B122" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>136012003</v>
       </c>
       <c r="B126" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>136012036</v>
       </c>
       <c r="B127" t="n">
-        <v>58608</v>
+        <v>58609</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>136012008</v>
       </c>
       <c r="B168" t="n">
-        <v>56551</v>
+        <v>56552</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>136011988</v>
       </c>
       <c r="B115" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>136012010</v>
       </c>
       <c r="B116" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>136012013</v>
       </c>
       <c r="B117" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136012022</v>
       </c>
       <c r="B120" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>136012027</v>
       </c>
       <c r="B121" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136012030</v>
       </c>
       <c r="B122" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>136012003</v>
       </c>
       <c r="B126" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>136012036</v>
       </c>
       <c r="B127" t="n">
-        <v>58609</v>
+        <v>58614</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>136012008</v>
       </c>
       <c r="B168" t="n">
-        <v>56552</v>
+        <v>56557</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>136011988</v>
       </c>
       <c r="B115" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>136012010</v>
       </c>
       <c r="B116" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>136012013</v>
       </c>
       <c r="B117" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136012022</v>
       </c>
       <c r="B120" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>136012027</v>
       </c>
       <c r="B121" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>136012030</v>
       </c>
       <c r="B122" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>136012003</v>
       </c>
       <c r="B126" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>136012036</v>
       </c>
       <c r="B127" t="n">
-        <v>58614</v>
+        <v>58627</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>136012008</v>
       </c>
       <c r="B168" t="n">
-        <v>56557</v>
+        <v>56570</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 33528-2026 artfynd.xlsx
+++ b/artfynd/A 33528-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011998</v>
       </c>
       <c r="B2" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136012019</v>
       </c>
       <c r="B3" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136012032</v>
       </c>
       <c r="B4" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136012016</v>
       </c>
       <c r="B5" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136012026</v>
       </c>
       <c r="B6" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136011985</v>
       </c>
       <c r="B78" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136011986</v>
       </c>
       <c r="B79" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136011990</v>
       </c>
       <c r="B80" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>136011996</v>
       </c>
       <c r="B81" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>136012006</v>
       </c>
       <c r="B82" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136012014</v>
       </c>
       <c r="B83" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>136012021</v>
       </c>
       <c r="B84" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>136012024</v>
       </c>
       <c r="B85" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>136012033</v>
       </c>
       <c r="B86" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>136011991</v>
       </c>
       <c r="B93" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>136012029</v>
       </c>
       <c r="B94" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
